--- a/data/trans_orig/P1438_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otro dolor crónico en 2023</t>
+          <t>Población con diagnóstico de otro dolor crónico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26726</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53095</t>
+          <t>54718</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477768</t>
+          <t>478673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493973</t>
+          <t>494323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414501</t>
+          <t>414273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429970</t>
+          <t>429719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>898866</t>
+          <t>897243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>921791</t>
+          <t>920276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16502</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27692</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>23989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39561</t>
+          <t>40118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435711</t>
+          <t>436176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445957</t>
+          <t>446125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354060</t>
+          <t>353872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366751</t>
+          <t>367246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>794404</t>
+          <t>793847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>811139</t>
+          <t>809976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49492</t>
+          <t>49305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>20902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69806</t>
+          <t>69539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618053</t>
+          <t>618240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657142</t>
+          <t>658167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142137</t>
+          <t>142577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154005</t>
+          <t>154370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764650</t>
+          <t>764917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815515</t>
+          <t>813554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49997</t>
+          <t>50247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78699</t>
+          <t>78251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75974</t>
+          <t>75309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82000</t>
+          <t>84698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139875</t>
+          <t>141970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>955158</t>
+          <t>955606</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>983860</t>
+          <t>983610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>902120</t>
+          <t>902785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951840</t>
+          <t>948221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1872076</t>
+          <t>1869981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1929951</t>
+          <t>1927253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72917</t>
+          <t>72257</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116253</t>
+          <t>114951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102579</t>
+          <t>101651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147078</t>
+          <t>147632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>432516</t>
+          <t>431845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>451944</t>
+          <t>452262</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722743</t>
+          <t>724045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>766079</t>
+          <t>766739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1165967</t>
+          <t>1165413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1210466</t>
+          <t>1211394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>56965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81464</t>
+          <t>81243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56674</t>
+          <t>56562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81738</t>
+          <t>83666</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235940</t>
+          <t>235012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679228</t>
+          <t>679449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>703225</t>
+          <t>703727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>919462</t>
+          <t>917534</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>944526</t>
+          <t>944638</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112700</t>
+          <t>118423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175351</t>
+          <t>177477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235745</t>
+          <t>235558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>315683</t>
+          <t>315957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>370451</t>
+          <t>376983</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>477896</t>
+          <t>475968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3197314</t>
+          <t>3195188</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3259965</t>
+          <t>3254242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3258229</t>
+          <t>3257955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3338167</t>
+          <t>3338354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6468681</t>
+          <t>6470609</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6576126</t>
+          <t>6569594</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1438_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Clase-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25821</t>
+          <t>30642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>27046</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19836</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37000</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>46258</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>34590</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>58320</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24253</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17748</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33194</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>41038</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>31685</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>54718</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>487709</t>
+          <t>530536</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>478673</t>
+          <t>519105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494323</t>
+          <t>537747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>423214</t>
+          <t>461365</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414273</t>
+          <t>451411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429719</t>
+          <t>468575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>910923</t>
+          <t>991900</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>897243</t>
+          <t>979838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>920276</t>
+          <t>1003568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504494</t>
+          <t>549747</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504494</t>
+          <t>549747</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504494</t>
+          <t>549747</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951961</t>
+          <t>1038158</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951961</t>
+          <t>1038158</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951961</t>
+          <t>1038158</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14506</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30931</t>
+          <t>32895</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40118</t>
+          <t>42723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>441922</t>
+          <t>472757</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>436176</t>
+          <t>467044</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>476955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>361112</t>
+          <t>399383</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353872</t>
+          <t>391815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367246</t>
+          <t>406150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>803034</t>
+          <t>872140</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>793847</t>
+          <t>862312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>809976</t>
+          <t>880493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381752</t>
+          <t>421823</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381752</t>
+          <t>421823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381752</t>
+          <t>421823</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833965</t>
+          <t>905035</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833965</t>
+          <t>905035</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833965</t>
+          <t>905035</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49305</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20902</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69539</t>
+          <t>64301</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>639310</t>
+          <t>440205</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618240</t>
+          <t>428422</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658167</t>
+          <t>449448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148774</t>
+          <t>167748</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142577</t>
+          <t>159742</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154370</t>
+          <t>173336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>788084</t>
+          <t>607954</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764917</t>
+          <t>593940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>813554</t>
+          <t>618324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62889</t>
+          <t>66311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50247</t>
+          <t>52132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78251</t>
+          <t>82697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>62727</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29873</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75309</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>118313</t>
+          <t>129038</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>110881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141970</t>
+          <t>147098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>970968</t>
+          <t>1064534</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>955606</t>
+          <t>1048148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>983610</t>
+          <t>1078713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>922670</t>
+          <t>798484</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>902785</t>
+          <t>785316</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>948221</t>
+          <t>810604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1893638</t>
+          <t>1863018</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1869981</t>
+          <t>1844958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1927253</t>
+          <t>1881175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033857</t>
+          <t>1130845</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033857</t>
+          <t>1130845</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033857</t>
+          <t>1130845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011951</t>
+          <t>1992056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011951</t>
+          <t>1992056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011951</t>
+          <t>1992056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42204</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>97242</t>
+          <t>105387</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72257</t>
+          <t>92250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114951</t>
+          <t>121275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>128089</t>
+          <t>137534</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101651</t>
+          <t>120104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147632</t>
+          <t>156057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>443201</t>
+          <t>534829</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431845</t>
+          <t>523504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>452262</t>
+          <t>543846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>741754</t>
+          <t>724740</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>724045</t>
+          <t>708852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>766739</t>
+          <t>737877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1184956</t>
+          <t>1259569</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1165413</t>
+          <t>1241046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1211394</t>
+          <t>1276999</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67749</t>
+          <t>74038</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>62088</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81243</t>
+          <t>89068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>68975</t>
+          <t>75256</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56562</t>
+          <t>62655</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83666</t>
+          <t>91362</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239281</t>
+          <t>236010</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235012</t>
+          <t>232990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>692943</t>
+          <t>769558</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679449</t>
+          <t>754528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>703727</t>
+          <t>781508</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>932225</t>
+          <t>1005568</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>917534</t>
+          <t>989462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>944638</t>
+          <t>1018169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>150273</t>
+          <t>159879</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118423</t>
+          <t>138592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>183516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>283445</t>
+          <t>311388</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235558</t>
+          <t>287432</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>315957</t>
+          <t>338248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>433719</t>
+          <t>471268</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>376983</t>
+          <t>437392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475968</t>
+          <t>506438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3222392</t>
+          <t>3278872</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3195188</t>
+          <t>3255235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3254242</t>
+          <t>3300159</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3290467</t>
+          <t>3321278</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3257955</t>
+          <t>3294418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3338354</t>
+          <t>3345234</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6512858</t>
+          <t>6600149</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6470609</t>
+          <t>6564979</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6569594</t>
+          <t>6634025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3372665</t>
+          <t>3438751</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3372665</t>
+          <t>3438751</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3372665</t>
+          <t>3438751</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573912</t>
+          <t>3632666</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573912</t>
+          <t>3632666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573912</t>
+          <t>3632666</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6946577</t>
+          <t>7071417</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6946577</t>
+          <t>7071417</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6946577</t>
+          <t>7071417</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
